--- a/old_new_models_results.xlsx
+++ b/old_new_models_results.xlsx
@@ -28682,14 +28682,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N34"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
@@ -28697,90 +28697,1378 @@
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="14" max="14" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>Results Summary — Original Prompt — Name Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t>Detected</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t>Succeeded</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t>Success rate</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t>Many-result runs</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" t="inlineStr" s="1">
-        <is>
-          <t>No results found</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>openai / gpt-5</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>openai / gpt-5-mini</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="1">
+        <is>
+          <t>Detailed Results — Original Prompt — Name Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="1">
+        <is>
+          <t>openai / gpt-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="2">
         <is>
           <t>File name</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B9" t="inlineStr" s="2">
         <is>
           <t>vision_ok</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="C9" t="inlineStr" s="2">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="2">
+      <c r="D9" t="inlineStr" s="2">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="2">
+      <c r="E9" t="inlineStr" s="2">
         <is>
           <t>x_px</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr" s="2">
+      <c r="F9" t="inlineStr" s="2">
         <is>
           <t>y_px</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr" s="2">
+      <c r="G9" t="inlineStr" s="2">
         <is>
           <t>dx_px</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr" s="2">
+      <c r="H9" t="inlineStr" s="2">
         <is>
           <t>dy_px</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr" s="2">
+      <c r="I9" t="inlineStr" s="2">
         <is>
           <t>error_px</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr" s="2">
+      <c r="J9" t="inlineStr" s="2">
         <is>
           <t>Succeeded</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr" s="2">
+      <c r="K9" t="inlineStr" s="2">
         <is>
           <t>residual_score</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr" s="2">
+      <c r="L9" t="inlineStr" s="2">
         <is>
           <t>inlier_score</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr" s="2">
+      <c r="M9" t="inlineStr" s="2">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr" s="2">
+      <c r="N9" t="inlineStr" s="2">
         <is>
           <t>Failure cause</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_34_06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>-136.511</v>
+      </c>
+      <c r="D10">
+        <v>-288.261</v>
+      </c>
+      <c r="E10">
+        <v>1327.056</v>
+      </c>
+      <c r="F10">
+        <v>906.421</v>
+      </c>
+      <c r="G10">
+        <v>-0.194</v>
+      </c>
+      <c r="H10">
+        <v>4.401</v>
+      </c>
+      <c r="I10">
+        <v>4.405</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_35_46</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>-136.294</v>
+      </c>
+      <c r="D11">
+        <v>-301.938</v>
+      </c>
+      <c r="E11">
+        <v>1327.007</v>
+      </c>
+      <c r="F11">
+        <v>903.309</v>
+      </c>
+      <c r="G11">
+        <v>-0.243</v>
+      </c>
+      <c r="H11">
+        <v>1.289</v>
+      </c>
+      <c r="I11">
+        <v>1.312</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_37_30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>-138.756</v>
+      </c>
+      <c r="D12">
+        <v>-295.636</v>
+      </c>
+      <c r="E12">
+        <v>1327.567</v>
+      </c>
+      <c r="F12">
+        <v>904.743</v>
+      </c>
+      <c r="G12">
+        <v>0.317</v>
+      </c>
+      <c r="H12">
+        <v>2.723</v>
+      </c>
+      <c r="I12">
+        <v>2.741</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>46</v>
+      </c>
+      <c r="L12">
+        <v>45</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="N12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_39_26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>-138.748</v>
+      </c>
+      <c r="D13">
+        <v>-307.877</v>
+      </c>
+      <c r="E13">
+        <v>1327.565</v>
+      </c>
+      <c r="F13">
+        <v>901.958</v>
+      </c>
+      <c r="G13">
+        <v>0.315</v>
+      </c>
+      <c r="H13">
+        <v>-0.062</v>
+      </c>
+      <c r="I13">
+        <v>0.321</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>35</v>
+      </c>
+      <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_41_24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>-138.748</v>
+      </c>
+      <c r="D14">
+        <v>-307.877</v>
+      </c>
+      <c r="E14">
+        <v>1327.565</v>
+      </c>
+      <c r="F14">
+        <v>901.958</v>
+      </c>
+      <c r="G14">
+        <v>0.315</v>
+      </c>
+      <c r="H14">
+        <v>-0.062</v>
+      </c>
+      <c r="I14">
+        <v>0.321</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>35</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_43_21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>-136.484</v>
+      </c>
+      <c r="D15">
+        <v>-305.768</v>
+      </c>
+      <c r="E15">
+        <v>1327.05</v>
+      </c>
+      <c r="F15">
+        <v>902.438</v>
+      </c>
+      <c r="G15">
+        <v>-0.2</v>
+      </c>
+      <c r="H15">
+        <v>0.418</v>
+      </c>
+      <c r="I15">
+        <v>0.463</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_44_51</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Error: No lines detected; Error: No line for input 2 detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_48_16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Error: No lines detected. Hough lines found no lines; Error: No line for input 1 detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_51_20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>-138.748</v>
+      </c>
+      <c r="D18">
+        <v>-307.877</v>
+      </c>
+      <c r="E18">
+        <v>1327.565</v>
+      </c>
+      <c r="F18">
+        <v>901.958</v>
+      </c>
+      <c r="G18">
+        <v>0.315</v>
+      </c>
+      <c r="H18">
+        <v>-0.062</v>
+      </c>
+      <c r="I18">
+        <v>0.321</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18">
+        <v>35</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5_20260826_14_52_53</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Error: No lines detected. Hough lines found no lines; Error: No line for input 1 detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="1">
+        <is>
+          <t>openai / gpt-5-mini</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="2">
+        <is>
+          <t>File name</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t>vision_ok</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="2">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="2">
+        <is>
+          <t>x_px</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="2">
+        <is>
+          <t>y_px</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr" s="2">
+        <is>
+          <t>dx_px</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr" s="2">
+        <is>
+          <t>dy_px</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr" s="2">
+        <is>
+          <t>error_px</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr" s="2">
+        <is>
+          <t>Succeeded</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr" s="2">
+        <is>
+          <t>residual_score</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr" s="2">
+        <is>
+          <t>inlier_score</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr" s="2">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr" s="2">
+        <is>
+          <t>Failure cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_14_56_02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>vision_ok is false; no point detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_14_57_45</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>-136.454</v>
+      </c>
+      <c r="D24">
+        <v>-296.519</v>
+      </c>
+      <c r="E24">
+        <v>1327.043</v>
+      </c>
+      <c r="F24">
+        <v>904.542</v>
+      </c>
+      <c r="G24">
+        <v>-0.207</v>
+      </c>
+      <c r="H24">
+        <v>2.522</v>
+      </c>
+      <c r="I24">
+        <v>2.53</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N24"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_14_58_51</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>-4293.88</v>
+      </c>
+      <c r="D25">
+        <v>-305.329</v>
+      </c>
+      <c r="E25">
+        <v>2272.856</v>
+      </c>
+      <c r="F25">
+        <v>902.538</v>
+      </c>
+      <c r="G25">
+        <v>945.606</v>
+      </c>
+      <c r="H25">
+        <v>0.518</v>
+      </c>
+      <c r="I25">
+        <v>945.606</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>10</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Pixel error 945.606 exceeds 6 px tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_14_59_47</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>-138.75</v>
+      </c>
+      <c r="D26">
+        <v>-304.618</v>
+      </c>
+      <c r="E26">
+        <v>1327.566</v>
+      </c>
+      <c r="F26">
+        <v>902.7</v>
+      </c>
+      <c r="G26">
+        <v>0.316</v>
+      </c>
+      <c r="H26">
+        <v>0.68</v>
+      </c>
+      <c r="I26">
+        <v>0.749</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26">
+        <v>41</v>
+      </c>
+      <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_15_00_44</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>-4293.476</v>
+      </c>
+      <c r="D27">
+        <v>-492.329</v>
+      </c>
+      <c r="E27">
+        <v>2272.764</v>
+      </c>
+      <c r="F27">
+        <v>859.995</v>
+      </c>
+      <c r="G27">
+        <v>945.514</v>
+      </c>
+      <c r="H27">
+        <v>-42.025</v>
+      </c>
+      <c r="I27">
+        <v>946.448</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>10</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Pixel error 946.448 exceeds 6 px tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_15_01_48</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>-4256.163</v>
+      </c>
+      <c r="D28">
+        <v>-267.329</v>
+      </c>
+      <c r="E28">
+        <v>2264.276</v>
+      </c>
+      <c r="F28">
+        <v>911.183</v>
+      </c>
+      <c r="G28">
+        <v>937.026</v>
+      </c>
+      <c r="H28">
+        <v>9.163</v>
+      </c>
+      <c r="I28">
+        <v>937.07</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>7</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Pixel error 937.070 exceeds 6 px tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_15_02_47</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>-4459.418</v>
+      </c>
+      <c r="D29">
+        <v>2305.968</v>
+      </c>
+      <c r="E29">
+        <v>2310.516</v>
+      </c>
+      <c r="F29">
+        <v>1496.607</v>
+      </c>
+      <c r="G29">
+        <v>983.266</v>
+      </c>
+      <c r="H29">
+        <v>594.587</v>
+      </c>
+      <c r="I29">
+        <v>1149.063</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29">
+        <v>60</v>
+      </c>
+      <c r="L29">
+        <v>25</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Pixel error 1149.063 exceeds 6 px tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_15_03_42</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>-136.465</v>
+      </c>
+      <c r="D30">
+        <v>-288.552</v>
+      </c>
+      <c r="E30">
+        <v>1327.046</v>
+      </c>
+      <c r="F30">
+        <v>906.354</v>
+      </c>
+      <c r="G30">
+        <v>-0.204</v>
+      </c>
+      <c r="H30">
+        <v>4.334</v>
+      </c>
+      <c r="I30">
+        <v>4.339</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_15_05_14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>2056.289</v>
+      </c>
+      <c r="D31">
+        <v>810.228</v>
+      </c>
+      <c r="E31">
+        <v>828.195</v>
+      </c>
+      <c r="F31">
+        <v>1156.327</v>
+      </c>
+      <c r="G31">
+        <v>-499.055</v>
+      </c>
+      <c r="H31">
+        <v>254.307</v>
+      </c>
+      <c r="I31">
+        <v>560.114</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Pixel error 560.114 exceeds 6 px tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>new models/corner/old models/name_only/sensor_corner_openai_gpt-5-mini_20260826_15_08_24</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>-4459.418</v>
+      </c>
+      <c r="D32">
+        <v>2305.968</v>
+      </c>
+      <c r="E32">
+        <v>2310.516</v>
+      </c>
+      <c r="F32">
+        <v>1496.607</v>
+      </c>
+      <c r="G32">
+        <v>983.266</v>
+      </c>
+      <c r="H32">
+        <v>594.587</v>
+      </c>
+      <c r="I32">
+        <v>1149.063</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32">
+        <v>60</v>
+      </c>
+      <c r="L32">
+        <v>25</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Pixel error 1149.063 exceeds 6 px tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
   </sheetData>
 </worksheet>
 </file>